--- a/数据/养殖客户档案.xlsx
+++ b/数据/养殖客户档案.xlsx
@@ -3560,7 +3560,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>9月10日/9月28日</t>
+          <t>9月10日/9月28日/10月13日</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3575,11 +3575,13 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>9月10日用户不在，电话联系测水打样；9月28日测水打样七两左右，鱼肥满度很好</t>
-        </is>
-      </c>
-      <c r="G69" t="n">
-        <v>2</v>
+          <t>9月10日用户不在，电话联系测水打样；9月28日测水打样七两左右，鱼肥满度很好；10月13日打样：鱼一斤三左右，长势好</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="H69" t="n">
         <v>45</v>

--- a/数据/养殖客户档案.xlsx
+++ b/数据/养殖客户档案.xlsx
@@ -3238,7 +3238,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>9月2日/9月7日/9月8日/9月12日/9月14日/9月17日/9月18日/9月21日/10月5日/10月7日</t>
+          <t>9月2日/9月7日/9月8日/9月12日/9月14日/9月17日/9月18日/9月21日/10月5日/10月7日/10月13日</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3253,11 +3253,13 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>9月2日测1、2、3、6、7号塘，2塘3塘亚盐偏高；9月7日转通威后测水打样：七号塘0.45455、六号塘0.45455、三号塘0.2；9月8日取回挂底渔网，打样一号塘0.5（大小匀称）、二号塘0.3125（大小不齐）；9月12日工人老板都不在；9月14日售后跟进（秋哥在溪尾基地不常来）；9月17日鱼塘出现死鱼，亚硝酸盐高达0.9严重超标，协助用降亚盐产品处理；9月18日回访复测：亚盐缓解、无死鱼、趋于好转；9月21日7号塘氨氮严重超标、6号塘亚盐偏高、部分塘口水面油膜；10月5日水质检测6口塘：3号塘氨氮0.50最高，5号塘亚盐0.28⚠️接近0.3需复检，4号塘亚盐0.25；10月7日大致坡基地（东路镇田尾泄）测7口塘：2号、3号塘亚盐超量程估0.8⚠️（暗深品红，鱼易浮头），已建议减料停餐、全天增氧、换水、泼盐，氨氮0.20-0.90正常</t>
-        </is>
-      </c>
-      <c r="G62" t="n">
-        <v>10</v>
+          <t>9月2日测1、2、3、6、7号塘，2塘3塘亚盐偏高；9月7日转通威后测水打样：七号塘0.45455、六号塘0.45455、三号塘0.2；9月8日取回挂底渔网，打样一号塘0.5（大小匀称）、二号塘0.3125（大小不齐）；9月12日工人老板都不在；9月14日售后跟进（秋哥在溪尾基地不常来）；9月17日鱼塘出现死鱼，亚硝酸盐高达0.9严重超标，协助用降亚盐产品处理；9月18日回访复测：亚盐缓解、无死鱼、趋于好转；9月21日7号塘氨氮严重超标、6号塘亚盐偏高、部分塘口水面油膜；10月5日水质检测6口塘：3号塘氨氮0.50最高，5号塘亚盐0.28⚠️接近0.3需复检，4号塘亚盐0.25；10月7日大致坡基地（东路镇田尾泄）测7口塘：2号、3号塘亚盐超量程估0.8⚠️（暗深品红，鱼易浮头），已建议减料停餐、全天增氧、换水、泼盐，氨氮0.20-0.90正常；10月13日测水客情服务（回访）</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="H62" t="n">
         <v>90</v>

--- a/数据/养殖客户档案.xlsx
+++ b/数据/养殖客户档案.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J115"/>
+  <dimension ref="A1:J116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>丁立强</t>
+          <t>丁力强</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>9月10日/9月21日/9月23日/9月27日/9月28日</t>
+          <t>9月10日/9月21日/9月23日/9月27日/9月28日/10月13日</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3625,11 +3625,11 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>9月10日希望建设光合菌扩培系统；9月21日有扩培光合菌需求，已自行联系吴老师对接；9月23日帮助用户泼洒我司动保；9月27日用完我司乳酸菌+芽孢分解菌后四天，鱼吃料情况稍差，测水正常，过几天不正常吃料则打样解剖；9月28日口塘测水打样五两，六号塘情况稍差、其余均良好</t>
+          <t>9月10日希望建设光合菌扩培系统；9月21日有扩培光合菌需求，已自行联系吴老师对接；9月23日帮助用户泼洒我司动保；9月27日用完我司乳酸菌+芽孢分解菌后四天，鱼吃料情况稍差，测水正常，过几天不正常吃料则打样解剖；9月28日口塘测水打样五两，六号塘情况稍差、其余均良好；10月13日基地客勤+测水10口塘：3号塘7.0/0.2/0.10、5号塘7.4/0.2/0.05、4号塘7.2/0.2/0.05、2号塘7.4/0.2/0.10、1号塘8.6/0.2/0.05（均西坡村）；6号塘7.2/0.40/0.10、10号塘7.4/0.20/0.10（信坡村）；7号塘7.2/0.90/0.05、8号塘7.4/0.90/0.10、9号塘7.2/0.90/0.10（南排坡），三项均正常，1号塘pH8.6经人眼复核确认；其余塘口待补测</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H70" t="n">
         <v>45</v>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>5次拜访；想建光合菌扩培系统、用我司乳酸菌+芽孢，技术服务粘性高</t>
+          <t>6次拜访；想建光合菌扩培系统、用我司乳酸菌+芽孢，技术服务粘性高</t>
         </is>
       </c>
     </row>
@@ -4944,12 +4944,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>9月27日</t>
+          <t>9月27日/10月13日</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>海一</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4959,11 +4959,11 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>用户对光合细菌培养很感兴趣，交流培养经验</t>
+          <t>用户对光合细菌培养很感兴趣，交流培养经验；10月13日客勤+测水1/2/4/3号塘（罗豆农场猪场）：pH7.4/7.2/7.2/7.2、氨氮0.5/0.9/0.9/0.2、亚盐0.05–0.10，三项均正常；另有4口塘已出完鱼（合计约8口塘）；与丁茂溪同用海一</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H99" t="n">
         <v>40</v>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>对光合细菌培养很感兴趣，交流培养经验，技术切入</t>
+          <t>2次拜访；对光合细菌培养很感兴趣、交流培养经验，技术切入；现用海一料</t>
         </is>
       </c>
     </row>
@@ -5692,6 +5692,52 @@
       <c r="J115" t="inlineStr">
         <is>
           <t>首次沟通后续用料，出现转化契机</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>梁修成</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>10月13日</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>海大2552</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>—（未提及）</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>10月13日走访（新名建档）：现用海大2552，仓库仍囤较多该料（刚到一批），近期无换料刚需；已约10月14日早测水。</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>1</v>
+      </c>
+      <c r="H116" t="n">
+        <v>40</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>C 有潜力</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>首次走访；现用海大2552、仓存充足，转化宜缓，做客情维护+测水服务切入</t>
         </is>
       </c>
     </row>

--- a/数据/养殖客户档案.xlsx
+++ b/数据/养殖客户档案.xlsx
@@ -3625,7 +3625,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>9月10日希望建设光合菌扩培系统；9月21日有扩培光合菌需求，已自行联系吴老师对接；9月23日帮助用户泼洒我司动保；9月27日用完我司乳酸菌+芽孢分解菌后四天，鱼吃料情况稍差，测水正常，过几天不正常吃料则打样解剖；9月28日口塘测水打样五两，六号塘情况稍差、其余均良好；10月13日基地客勤+测水10口塘：3号塘7.0/0.2/0.10、5号塘7.4/0.2/0.05、4号塘7.2/0.2/0.05、2号塘7.4/0.2/0.10、1号塘8.6/0.2/0.05（均西坡村）；6号塘7.2/0.40/0.10、10号塘7.4/0.20/0.10（信坡村）；7号塘7.2/0.90/0.05、8号塘7.4/0.90/0.10、9号塘7.2/0.90/0.10（南排坡），三项均正常，1号塘pH8.6经人眼复核确认；其余塘口待补测</t>
+          <t>9月10日希望建设光合菌扩培系统；9月21日有扩培光合菌需求，已自行联系吴老师对接；9月23日帮助用户泼洒我司动保；9月27日用完我司乳酸菌+芽孢分解菌后四天，鱼吃料情况稍差，测水正常，过几天不正常吃料则打样解剖；9月28日口塘测水打样五两，六号塘情况稍差、其余均良好；10月13日基地客勤+测水10口塘：3号塘7.0/0.2/0.10、5号塘7.4/0.2/0.005、4号塘7.2/0.2/0.005、2号塘7.4/0.2/0.10、1号塘8.6/0.2/0.005（均西坡村）；6号塘7.2/0.40/0.10、10号塘7.4/0.20/0.10（信坡村）；7号塘7.2/0.90/0.05、8号塘7.4/0.90/0.10、9号塘7.2/0.90/0.10（南排坡），三项均正常，1号塘pH8.6经人眼复核确认；其余塘口待补测</t>
         </is>
       </c>
       <c r="G70" t="n">

--- a/数据/养殖客户档案.xlsx
+++ b/数据/养殖客户档案.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J116"/>
+  <dimension ref="A1:J122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -677,7 +677,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>二两鱼</t>
+          <t>二两鱼。10月15日：基地与云维军基地合并（用户口述「冯学兴」，同音变体）。</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>9月10日/9月21日/9月23日/9月27日/9月28日/10月13日</t>
+          <t>9月10日/9月21日/9月23日/9月27日/9月28日/10月13日/10月14日</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3625,11 +3625,11 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>9月10日希望建设光合菌扩培系统；9月21日有扩培光合菌需求，已自行联系吴老师对接；9月23日帮助用户泼洒我司动保；9月27日用完我司乳酸菌+芽孢分解菌后四天，鱼吃料情况稍差，测水正常，过几天不正常吃料则打样解剖；9月28日口塘测水打样五两，六号塘情况稍差、其余均良好；10月13日基地客勤+测水10口塘：3号塘7.0/0.2/0.10、5号塘7.4/0.2/0.005、4号塘7.2/0.2/0.005、2号塘7.4/0.2/0.10、1号塘8.6/0.2/0.005（均西坡村）；6号塘7.2/0.40/0.10、10号塘7.4/0.20/0.10（信坡村）；7号塘7.2/0.90/0.05、8号塘7.4/0.90/0.10、9号塘7.2/0.90/0.10（南排坡），三项均正常，1号塘pH8.6经人眼复核确认；其余塘口待补测</t>
+          <t>9月10日希望建设光合菌扩培系统；9月21日有扩培光合菌需求，已自行联系吴老师对接；9月23日帮助用户泼洒我司动保；9月27日用完我司乳酸菌+芽孢分解菌后四天，鱼吃料情况稍差，测水正常，过几天不正常吃料则打样解剖；9月28日口塘测水打样五两，六号塘情况稍差、其余均良好；10月13日基地客勤+测水10口塘：3号塘7.0/0.2/0.10、5号塘7.4/0.2/0.005、4号塘7.2/0.2/0.005、2号塘7.4/0.2/0.10、1号塘8.6/0.2/0.005（均西坡村）；6号塘7.2/0.40/0.10、10号塘7.4/0.20/0.10（信坡村）；7号塘7.2/0.90/0.05、8号塘7.4/0.90/0.10、9号塘7.2/0.90/0.10（南排坡），三项均正常，1号塘pH8.6经人眼复核确认；其余塘口待补测；10月14日：协助马总放石斑进塘</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H70" t="n">
         <v>45</v>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>10月12日</t>
+          <t>10月12日/10月14日</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5675,11 +5675,11 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>10.12客情走访：沟通后续用料问题（与潘如军为不同人，用户明确区分）。新增。</t>
+          <t>10.12客情走访：沟通后续用料问题（与潘如军为不同人，用户明确区分）。新增。10月14日回访：反映黑黄料问题，料塔迟迟未动工；黑黄料涉及饲料品牌与批次待取样核实，料塔未动工原因与预计工期待跟进。</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H115" t="n">
         <v>20</v>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>10月13日</t>
+          <t>10月13日/10月14日</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5721,11 +5721,11 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>10月13日走访（新名建档）：现用海大2552，仓库仍囤较多该料（刚到一批），近期无换料刚需；已约10月14日早测水。</t>
+          <t>10月13日走访（新名建档）：现用海大2552，仓库仍囤较多该料（刚到一批），近期无换料刚需；已约10月14日早测水。10月14日拜访：用料情况同樊法云，用到一半打样效果不好即停。10月15日走访中获悉：存塘罗非50万苗。</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H116" t="n">
         <v>40</v>
@@ -5738,6 +5738,282 @@
       <c r="J116" t="inlineStr">
         <is>
           <t>首次走访；现用海大2552、仓存充足，转化宜缓，做客情维护+测水服务切入</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>吴焕亮</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>10月15日</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>—（未提及）</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>—（未提及）</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>10月15日客情走访（新名建档）。</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>1</v>
+      </c>
+      <c r="H117" t="n">
+        <v>20</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>C 有潜力</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>首次走访，用料情况待摸</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>云维军</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>10月15日</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>—（未提及）</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>—（未提及）</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>10月15日客情走访（新名建档）：基地与冯学新基地合并（用户口述「冯学兴」，同音变体）。</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>1</v>
+      </c>
+      <c r="H118" t="n">
+        <v>20</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>C 有潜力</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>首次走访；基地合并，规模待摸</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>郑国庆</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>10月15日</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>—（未提及）</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>—（未提及）</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>10月15日客情走访（新名建档）。</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>1</v>
+      </c>
+      <c r="H119" t="n">
+        <v>20</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>C 有潜力</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>首次走访，用料情况待摸</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>丁旭华</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>10月15日</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>—（未提及）</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>—（未提及）</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>10月15日客情走访（新名建档）：存塘约20万苗，计划2027年4月抓鱼；这一造鱼大的7两左右、小的6两左右。</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>1</v>
+      </c>
+      <c r="H120" t="n">
+        <v>25</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>C 有潜力</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>首次走访；下一造拿料节点约在2027年4月出鱼后</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>樊法云</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>10月14日/10月15日</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>海一、海大</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>—（未提及）</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>10月14日走访：现用海一、海大，之前拉过通威、打样效果不好也没全程用，换料接受度低。10月15日走访中获悉：存塘罗非30万苗（用户本次记作「樊法元」，同音变体）。</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>2</v>
+      </c>
+      <c r="H121" t="n">
+        <v>15</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>C 有潜力</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>曾试通威打样半途而废；换料接受度低，待下一批拿料节点</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>王焕忠</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>10月14日</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>—（未提及）</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>—（未提及）</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>10月14日走访（新名建档）：用料情况同樊法云，用到一半打样效果不好即停；混料差异难看出谁家饲料更好或者更次，打样不彻底则对比无据、转化无发力点。</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>1</v>
+      </c>
+      <c r="H122" t="n">
+        <v>20</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>C 有潜力</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>首次走访；打样半途而废，客情铺垫待加强</t>
         </is>
       </c>
     </row>

--- a/数据/养殖客户档案.xlsx
+++ b/数据/养殖客户档案.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J122"/>
+  <dimension ref="A1:J123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>9月2日/9月7日/9月8日/9月12日/9月14日/9月17日/9月18日/9月21日/10月5日/10月7日/10月13日</t>
+          <t>9月2日/9月7日/9月8日/9月12日/9月14日/9月17日/9月18日/9月21日/10月5日/10月7日/10月13日/10月16日</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>9月2日测1、2、3、6、7号塘，2塘3塘亚盐偏高；9月7日转通威后测水打样：七号塘0.45455、六号塘0.45455、三号塘0.2；9月8日取回挂底渔网，打样一号塘0.5（大小匀称）、二号塘0.3125（大小不齐）；9月12日工人老板都不在；9月14日售后跟进（秋哥在溪尾基地不常来）；9月17日鱼塘出现死鱼，亚硝酸盐高达0.9严重超标，协助用降亚盐产品处理；9月18日回访复测：亚盐缓解、无死鱼、趋于好转；9月21日7号塘氨氮严重超标、6号塘亚盐偏高、部分塘口水面油膜；10月5日水质检测6口塘：3号塘氨氮0.50最高，5号塘亚盐0.28⚠️接近0.3需复检，4号塘亚盐0.25；10月7日大致坡基地（东路镇田尾泄）测7口塘：2号、3号塘亚盐超量程估0.8⚠️（暗深品红，鱼易浮头），已建议减料停餐、全天增氧、换水、泼盐，氨氮0.20-0.90正常；10月13日测水客情服务（回访）</t>
+          <t>9月2日测1、2、3、6、7号塘，2塘3塘亚盐偏高；9月7日转通威后测水打样：七号塘0.45455、六号塘0.45455、三号塘0.2；9月8日取回挂底渔网，打样一号塘0.5（大小匀称）、二号塘0.3125（大小不齐）；9月12日工人老板都不在；9月14日售后跟进（秋哥在溪尾基地不常来）；9月17日鱼塘出现死鱼，亚硝酸盐高达0.9严重超标，协助用降亚盐产品处理；9月18日回访复测：亚盐缓解、无死鱼、趋于好转；9月21日7号塘氨氮严重超标、6号塘亚盐偏高、部分塘口水面油膜；10月5日水质检测6口塘：3号塘氨氮0.50最高，5号塘亚盐0.28⚠️接近0.3需复检，4号塘亚盐0.25；10月7日大致坡基地（东路镇田尾泄）测7口塘：2号、3号塘亚盐超量程估0.8⚠️（暗深品红，鱼易浮头），已建议减料停餐、全天增氧、换水、泼盐，氨氮0.20-0.90正常；10月13日测水客情服务（回访）；10月16日大致坡基地第三轮打样：1号1.02、2号0.81、3号0.77、4号0.53、5号0.54、6号0.99、7号0.83斤/条，较9月29日涨0.17-0.31，1号过斤；交谈后续用料计划；查阅8-10月投料台账，用量持续攀升，10月日均约76包</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H62" t="n">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>9月10日/9月28日/10月13日</t>
+          <t>9月10日/9月28日/10月13日/10月16日</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3577,12 +3577,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>9月10日用户不在，电话联系测水打样；9月28日测水打样七两左右，鱼肥满度很好；10月13日打样：鱼一斤三左右，长势好</t>
+          <t>9月10日用户不在，电话联系测水打样；9月28日测水打样七两左右，鱼肥满度很好；10月13日打样：鱼一斤三左右，长势好；10月16日走访，今日未打样，约定10月23日再来打样测水（底下那口塘）</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H69" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>10月9日</t>
+          <t>10月9日/10月16日</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5309,11 +5309,11 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>拜访，用户不愿意交谈</t>
+          <t>拜访，用户不愿意交谈；10月16日走访未遇本人，去接小孩</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H107" t="n">
         <v>3</v>
@@ -6014,6 +6014,52 @@
       <c r="J122" t="inlineStr">
         <is>
           <t>首次走访；打样半途而废，客情铺垫待加强</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>榆林舰</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>10月16日</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>—（未提及）</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>—（未提及）</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>10月16日走访（新接触），详情待补</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>1</v>
+      </c>
+      <c r="H123" t="n">
+        <v>20</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>C 有潜力</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>首次走访，详情待摸</t>
         </is>
       </c>
     </row>

--- a/数据/养殖客户档案.xlsx
+++ b/数据/养殖客户档案.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J123"/>
+  <dimension ref="A1:J126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>9月2日/9月7日/9月8日/9月12日/9月14日/9月17日/9月18日/9月21日/10月5日/10月7日/10月13日/10月16日</t>
+          <t>9月2日/9月7日/9月8日/9月12日/9月14日/9月17日/9月18日/9月21日/10月5日/10月7日/10月13日/10月16日/10月19日</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3253,13 +3253,11 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>9月2日测1、2、3、6、7号塘，2塘3塘亚盐偏高；9月7日转通威后测水打样：七号塘0.45455、六号塘0.45455、三号塘0.2；9月8日取回挂底渔网，打样一号塘0.5（大小匀称）、二号塘0.3125（大小不齐）；9月12日工人老板都不在；9月14日售后跟进（秋哥在溪尾基地不常来）；9月17日鱼塘出现死鱼，亚硝酸盐高达0.9严重超标，协助用降亚盐产品处理；9月18日回访复测：亚盐缓解、无死鱼、趋于好转；9月21日7号塘氨氮严重超标、6号塘亚盐偏高、部分塘口水面油膜；10月5日水质检测6口塘：3号塘氨氮0.50最高，5号塘亚盐0.28⚠️接近0.3需复检，4号塘亚盐0.25；10月7日大致坡基地（东路镇田尾泄）测7口塘：2号、3号塘亚盐超量程估0.8⚠️（暗深品红，鱼易浮头），已建议减料停餐、全天增氧、换水、泼盐，氨氮0.20-0.90正常；10月13日测水客情服务（回访）；10月16日大致坡基地第三轮打样：1号1.02、2号0.81、3号0.77、4号0.53、5号0.54、6号0.99、7号0.83斤/条，较9月29日涨0.17-0.31，1号过斤；交谈后续用料计划；查阅8-10月投料台账，用量持续攀升，10月日均约76包</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+          <t>9月2日测1、2、3、6、7号塘，2塘3塘亚盐偏高；9月7日转通威后测水打样：七号塘0.45455、六号塘0.45455、三号塘0.2；9月8日取回挂底渔网，打样一号塘0.5（大小匀称）、二号塘0.3125（大小不齐）；9月12日工人老板都不在；9月14日售后跟进（秋哥在溪尾基地不常来）；9月17日鱼塘出现死鱼，亚硝酸盐高达0.9严重超标，协助用降亚盐产品处理；9月18日回访复测：亚盐缓解、无死鱼、趋于好转；9月21日7号塘氨氮严重超标、6号塘亚盐偏高、部分塘口水面油膜；10月5日水质检测6口塘：3号塘氨氮0.50最高，5号塘亚盐0.28⚠️接近0.3需复检，4号塘亚盐0.25；10月7日大致坡基地（东路镇田尾泄）测7口塘：2号、3号塘亚盐超量程估0.8⚠️（暗深品红，鱼易浮头），已建议减料停餐、全天增氧、换水、泼盐，氨氮0.20-0.90正常；10月13日测水客情服务（回访）；10月16日大致坡基地第三轮打样：1号1.02、2号0.81、3号0.77、4号0.53、5号0.54、6号0.99、7号0.83斤/条，较9月29日涨0.17-0.31，1号过斤；交谈后续用料计划；查阅8-10月投料台账，用量持续攀升，10月日均约76包；10月19日大致坡基地打样，解答该基地鱼长势偏慢的疑问；4号塘计划本月底出鱼，后续跟进出鱼安排与用料情况</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>13</v>
       </c>
       <c r="H62" t="n">
         <v>90</v>
@@ -3562,7 +3560,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>9月10日/9月28日/10月13日/10月16日</t>
+          <t>9月10日/9月28日/10月13日/10月16日/10月23日</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3577,13 +3575,11 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>9月10日用户不在，电话联系测水打样；9月28日测水打样七两左右，鱼肥满度很好；10月13日打样：鱼一斤三左右，长势好；10月16日走访，今日未打样，约定10月23日再来打样测水（底下那口塘）</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+          <t>9月10日用户不在，电话联系测水打样；9月28日测水打样七两左右，鱼肥满度很好；10月13日打样：鱼一斤三左右，长势好；10月16日走访，今日未打样，约定10月23日再来打样测水（底下那口塘）；10月23日打样测水：塘号结构1号苗塘、2号中间那口、3号路边塘；1号塘10月21日放苗14万尾、亚盐偏高0.3左右踩报警线；2号塘条均八两、存塘鱼7万尾；3号塘条均预计1.4斤以上（10月13日1.35斤）、存塘未知；2号3号水质正常</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>5</v>
       </c>
       <c r="H69" t="n">
         <v>45</v>
@@ -3610,7 +3606,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>9月10日/9月21日/9月23日/9月27日/9月28日/10月13日/10月14日</t>
+          <t>9月10日/9月21日/9月23日/9月27日/9月28日/10月13日/10月14日/10月23日</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3625,11 +3621,11 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>9月10日希望建设光合菌扩培系统；9月21日有扩培光合菌需求，已自行联系吴老师对接；9月23日帮助用户泼洒我司动保；9月27日用完我司乳酸菌+芽孢分解菌后四天，鱼吃料情况稍差，测水正常，过几天不正常吃料则打样解剖；9月28日口塘测水打样五两，六号塘情况稍差、其余均良好；10月13日基地客勤+测水10口塘：3号塘7.0/0.2/0.10、5号塘7.4/0.2/0.005、4号塘7.2/0.2/0.005、2号塘7.4/0.2/0.10、1号塘8.6/0.2/0.005（均西坡村）；6号塘7.2/0.40/0.10、10号塘7.4/0.20/0.10（信坡村）；7号塘7.2/0.90/0.05、8号塘7.4/0.90/0.10、9号塘7.2/0.90/0.10（南排坡），三项均正常，1号塘pH8.6经人眼复核确认；其余塘口待补测；10月14日：协助马总放石斑进塘</t>
+          <t>9月10日希望建设光合菌扩培系统；9月21日有扩培光合菌需求，已自行联系吴老师对接；9月23日帮助用户泼洒我司动保；9月27日用完我司乳酸菌+芽孢分解菌后四天，鱼吃料情况稍差，测水正常，过几天不正常吃料则打样解剖；9月28日口塘测水打样五两，六号塘情况稍差、其余均良好；10月13日基地客勤+测水10口塘：3号塘7.0/0.2/0.10、5号塘7.4/0.2/0.005、4号塘7.2/0.2/0.005、2号塘7.4/0.2/0.10、1号塘8.6/0.2/0.005（均西坡村）；6号塘7.2/0.40/0.10、10号塘7.4/0.20/0.10（信坡村）；7号塘7.2/0.90/0.05、8号塘7.4/0.90/0.10、9号塘7.2/0.90/0.10（南排坡），三项均正常，1号塘pH8.6经人眼复核确认；其余塘口待补测；10月14日：协助马总放石斑进塘；10月23日积炭素累计用到100包，今天拉了33包</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H70" t="n">
         <v>45</v>
@@ -3886,7 +3882,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>10月9日</t>
+          <t>10月9日/10月17日</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3901,11 +3897,11 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>10.09走访：用料已更换，现小料唐人神、大料天翔819（挂账价114，属低档料，判断难养出效果）；此前用添祥、海大料，跟添祥、郑海杰拿料，现跟谁拿料待问清；鱼苗和大头混养，宝路苗，鱼现八两左右，预计11月初出鱼；出鱼后回访核实包产</t>
+          <t>10.09走访：用料已更换，现小料唐人神、大料天翔819（挂账价114，属低档料，判断难养出效果）；此前用添祥、海大料，跟添祥、郑海杰拿料，现跟谁拿料待问清；鱼苗和大头混养，宝路苗，鱼现八两左右，预计11月初出鱼；出鱼后回访核实包产；10月17日沟通转料：用户口述现用天祥料价格113（同音变体：天翔819），与我司产品价格层级不符，转料非常困难，后续继续跟进</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H76" t="n">
         <v>8</v>
@@ -5997,7 +5993,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>10月14日走访（新名建档）：用料情况同樊法云，用到一半打样效果不好即停；混料差异难看出谁家饲料更好或者更次，打样不彻底则对比无据、转化无发力点。</t>
+          <t>10月14日走访（新名建档）：用料情况同樊法云，用到一半打样效果不好即停；混料差异难看出谁家饲料更好或者更次，打样不彻底则对比无据、转化无发力点。；10月23日渠道线索：给王卫明供海大2552料，角色从养殖户延伸至经手供料</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -6060,6 +6056,144 @@
       <c r="J123" t="inlineStr">
         <is>
           <t>首次走访，详情待摸</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>陈老板</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>10月19日</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>—（未提及）</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>—（未提及）</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>10月19日走访（新接触）：养殖叉尾，维护客情，基本情况待跟进；与塔楼区域叉尾养户是否同批待核实</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>1</v>
+      </c>
+      <c r="H124" t="n">
+        <v>20</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>C 有潜力</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>首次接触，叉尾养殖，客情维护中</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>王卫明</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>10月22日</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>海大2552</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>王焕忠</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>10月22日拜访（新接触）：存塘鱼八两左右，之前用百洋料，这一造全程用海大，说明年用料再考虑通威</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>1</v>
+      </c>
+      <c r="H125" t="n">
+        <v>20</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>C 有潜力</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>首次接触，下一造有通威转化意向</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>徐在苏</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>10月22日/10月23日</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>—（未提及）</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>—（未提及）</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>10月22日走访：老板休息，约次日看抓鱼；10月23日抓鱼回访：一号塘包产35（死鱼严重）、二号塘包产38、三号塘未抓完；老徐自述包产不过40系鱼苗问题</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>2</v>
+      </c>
+      <c r="H126" t="n">
+        <v>20</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>C 有潜力</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>首次回访拿到包产数据，用户归因苗种，存服务切入点</t>
         </is>
       </c>
     </row>

--- a/数据/养殖客户档案.xlsx
+++ b/数据/养殖客户档案.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J126"/>
+  <dimension ref="A1:J127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>9月4日/9月10日/9月16日/9月21日/10月6日</t>
+          <t>9月4日/9月10日/9月16日/9月21日/10月6日/10月24日</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3207,11 +3207,11 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>通威老用户：9月4日对1号、2号鱼塘测水；9月10日、9月21日正常客勤走访/测水；9月16日用通威9912饲料，合作稳定；10月6日水质检测3口塘：①号塘氨氮8⚠️（高量程，今日全场最高，重点跟踪），②号塘0.60、③号塘0.90</t>
+          <t>通威老用户：9月4日对1号、2号鱼塘测水；9月10日、9月21日正常客勤走访/测水；9月16日用通威9912饲料，合作稳定；10月6日水质检测3口塘：①号塘氨氮8⚠️（高量程，今日全场最高，重点跟踪），②号塘0.60、③号塘0.9010月24日：今天抓鱼，前往看情况，出鱼中，出完再联系。</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H61" t="n">
         <v>95</v>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>9月2日/10月10日</t>
+          <t>9月2日/10月10日/10月24日</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3299,11 +3299,11 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>基本全程用翔泰、拉过一车通威；反映翔泰长得不行，后两月冲重量想拉通威但经销商马津深不给拉；准备拿苗原13号推迟至16号；5口塘多处亚盐偏高；其弟丁开福苗塘放60万苗（约4800尾/斤），趁早刺激快速转料用开口乐。10.10客情走访。</t>
+          <t>基本全程用翔泰、拉过一车通威；反映翔泰长得不行，后两月冲重量想拉通威但经销商马津深不给拉；准备拿苗原13号推迟至16号；5口塘多处亚盐偏高；其弟丁开福苗塘放60万苗（约4800尾/斤），趁早刺激快速转料用开口乐。10.10客情走访。10月24日：测水，3号塘pH8.0（鱼苗塘，已拿苗50万尾）；6号塘氨氮、亚盐双高⚠️，需2天内复测取具体数值并给调水建议；打样：2号塘八两、4号塘一斤、5号塘一斤、6号塘8两（6号塘规格偏小）。</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H63" t="n">
         <v>35</v>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>9月10日/9月21日/9月23日/9月27日/9月28日/10月13日/10月14日/10月23日</t>
+          <t>9月10日/9月21日/9月23日/9月27日/9月28日/10月13日/10月14日/10月23日/10月25日</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>9月10日希望建设光合菌扩培系统；9月21日有扩培光合菌需求，已自行联系吴老师对接；9月23日帮助用户泼洒我司动保；9月27日用完我司乳酸菌+芽孢分解菌后四天，鱼吃料情况稍差，测水正常，过几天不正常吃料则打样解剖；9月28日口塘测水打样五两，六号塘情况稍差、其余均良好；10月13日基地客勤+测水10口塘：3号塘7.0/0.2/0.10、5号塘7.4/0.2/0.005、4号塘7.2/0.2/0.005、2号塘7.4/0.2/0.10、1号塘8.6/0.2/0.005（均西坡村）；6号塘7.2/0.40/0.10、10号塘7.4/0.20/0.10（信坡村）；7号塘7.2/0.90/0.05、8号塘7.4/0.90/0.10、9号塘7.2/0.90/0.10（南排坡），三项均正常，1号塘pH8.6经人眼复核确认；其余塘口待补测；10月14日：协助马总放石斑进塘；10月23日积炭素累计用到100包，今天拉了33包</t>
+          <t>9月10日希望建设光合菌扩培系统；9月21日有扩培光合菌需求，已自行联系吴老师对接；9月23日帮助用户泼洒我司动保；9月27日用完我司乳酸菌+芽孢分解菌后四天，鱼吃料情况稍差，测水正常，过几天不正常吃料则打样解剖；9月28日口塘测水打样五两，六号塘情况稍差、其余均良好；10月13日基地客勤+测水10口塘：3号塘7.0/0.2/0.10、5号塘7.4/0.2/0.005、4号塘7.2/0.2/0.005、2号塘7.4/0.2/0.10、1号塘8.6/0.2/0.005（均西坡村）；6号塘7.2/0.40/0.10、10号塘7.4/0.20/0.10（信坡村）；7号塘7.2/0.90/0.05、8号塘7.4/0.90/0.10、9号塘7.2/0.90/0.10（南排坡），三项均正常，1号塘pH8.6经人眼复核确认；其余塘口待补测；10月14日：协助马总放石斑进塘；10月23日积炭素累计用到100包，今天拉了33包10月25日：送冻宝和药物，客情维护。</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H70" t="n">
         <v>45</v>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>10月15日</t>
+          <t>10月15日/10月25日</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5804,16 +5804,16 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>—（未提及）</t>
+          <t>冯学新</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>10月15日客情走访（新名建档）：基地与冯学新基地合并（用户口述「冯学兴」，同音变体）。</t>
+          <t>10月15日客情走访（新名建档）：基地与冯学新基地合并（用户口述「冯学兴」，同音变体）。10月25日：拿料受限于冯学新。</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H118" t="n">
         <v>20</v>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>10月15日</t>
+          <t>10月15日/10月24日/10月25日</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5901,11 +5901,11 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>10月15日客情走访（新名建档）：存塘约20万苗，计划2027年4月抓鱼；这一造鱼大的7两左右、小的6两左右。</t>
+          <t>10月15日客情走访（新名建档）：存塘约20万苗，计划2027年4月抓鱼；这一造鱼大的7两左右、小的6两左右。10月24日：用户要求打样，查看酵益宝养殖情况。10月25日：对接打样，案例佐证酵益宝效果。</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H120" t="n">
         <v>25</v>
@@ -6194,6 +6194,52 @@
       <c r="J126" t="inlineStr">
         <is>
           <t>首次回访拿到包产数据，用户归因苗种，存服务切入点</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>施锦云</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>10月25日</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>—（未提及）</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>—（未提及）</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>10月25日首次拜访，用户不在，基本情况待了解。</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>1</v>
+      </c>
+      <c r="H127" t="n">
+        <v>20</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>C 有潜力</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>首次拜访，用户不在，基本情况待了解</t>
         </is>
       </c>
     </row>

--- a/数据/养殖客户档案.xlsx
+++ b/数据/养殖客户档案.xlsx
@@ -3207,7 +3207,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>通威老用户：9月4日对1号、2号鱼塘测水；9月10日、9月21日正常客勤走访/测水；9月16日用通威9912饲料，合作稳定；10月6日水质检测3口塘：①号塘氨氮8⚠️（高量程，今日全场最高，重点跟踪），②号塘0.60、③号塘0.9010月24日：今天抓鱼，前往看情况，出鱼中，出完再联系。</t>
+          <t>通威老用户：9月4日对1号、2号鱼塘测水；9月10日、9月21日正常客勤走访/测水；9月16日用通威9912饲料，合作稳定；10月6日水质检测3口塘：①号塘氨氮8⚠️（高量程，今日全场最高，重点跟踪），②号塘0.60、③号塘0.90；10月24日：今天抓鱼，前往看情况，出鱼中，出完再联系。</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>9月10日希望建设光合菌扩培系统；9月21日有扩培光合菌需求，已自行联系吴老师对接；9月23日帮助用户泼洒我司动保；9月27日用完我司乳酸菌+芽孢分解菌后四天，鱼吃料情况稍差，测水正常，过几天不正常吃料则打样解剖；9月28日口塘测水打样五两，六号塘情况稍差、其余均良好；10月13日基地客勤+测水10口塘：3号塘7.0/0.2/0.10、5号塘7.4/0.2/0.005、4号塘7.2/0.2/0.005、2号塘7.4/0.2/0.10、1号塘8.6/0.2/0.005（均西坡村）；6号塘7.2/0.40/0.10、10号塘7.4/0.20/0.10（信坡村）；7号塘7.2/0.90/0.05、8号塘7.4/0.90/0.10、9号塘7.2/0.90/0.10（南排坡），三项均正常，1号塘pH8.6经人眼复核确认；其余塘口待补测；10月14日：协助马总放石斑进塘；10月23日积炭素累计用到100包，今天拉了33包10月25日：送冻宝和药物，客情维护。</t>
+          <t>9月10日希望建设光合菌扩培系统；9月21日有扩培光合菌需求，已自行联系吴老师对接；9月23日帮助用户泼洒我司动保；9月27日用完我司乳酸菌+芽孢分解菌后四天，鱼吃料情况稍差，测水正常，过几天不正常吃料则打样解剖；9月28日口塘测水打样五两，六号塘情况稍差、其余均良好；10月13日基地客勤+测水10口塘：3号塘7.0/0.2/0.10、5号塘7.4/0.2/0.005、4号塘7.2/0.2/0.005、2号塘7.4/0.2/0.10、1号塘8.6/0.2/0.005（均西坡村）；6号塘7.2/0.40/0.10、10号塘7.4/0.20/0.10（信坡村）；7号塘7.2/0.90/0.05、8号塘7.4/0.90/0.10、9号塘7.2/0.90/0.10（南排坡），三项均正常，1号塘pH8.6经人眼复核确认；其余塘口待补测；10月14日：协助马总放石斑进塘；10月23日积炭素累计用到100包，今天拉了33包；10月25日：送冻宝和药物，客情维护。</t>
         </is>
       </c>
       <c r="G70" t="n">

--- a/数据/养殖客户档案.xlsx
+++ b/数据/养殖客户档案.xlsx
@@ -6203,7 +6203,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>施锦云</t>
+          <t>施景云</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">

--- a/数据/养殖客户档案.xlsx
+++ b/数据/养殖客户档案.xlsx
@@ -3621,7 +3621,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>9月10日希望建设光合菌扩培系统；9月21日有扩培光合菌需求，已自行联系吴老师对接；9月23日帮助用户泼洒我司动保；9月27日用完我司乳酸菌+芽孢分解菌后四天，鱼吃料情况稍差，测水正常，过几天不正常吃料则打样解剖；9月28日口塘测水打样五两，六号塘情况稍差、其余均良好；10月13日基地客勤+测水10口塘：3号塘7.0/0.2/0.10、5号塘7.4/0.2/0.005、4号塘7.2/0.2/0.005、2号塘7.4/0.2/0.10、1号塘8.6/0.2/0.005（均西坡村）；6号塘7.2/0.40/0.10、10号塘7.4/0.20/0.10（信坡村）；7号塘7.2/0.90/0.05、8号塘7.4/0.90/0.10、9号塘7.2/0.90/0.10（南排坡），三项均正常，1号塘pH8.6经人眼复核确认；其余塘口待补测；10月14日：协助马总放石斑进塘；10月23日积炭素累计用到100包，今天拉了33包；10月25日：送冻宝和药物，客情维护。</t>
+          <t>9月10日希望建设光合菌扩培系统；9月21日有扩培光合菌需求，已自行联系吴老师对接；9月23日帮助用户泼洒我司动保；9月27日用完我司乳酸菌+芽孢分解菌后四天，鱼吃料情况稍差，测水正常，过几天不正常吃料则打样解剖；9月28日口塘测水打样五两，六号塘情况稍差、其余均良好；10月13日基地客勤+测水10口塘：3号塘7.0/0.2/0.10、5号塘7.4/0.2/0.005、4号塘7.2/0.2/0.005、2号塘7.4/0.2/0.10、1号塘8.6/0.2/0.005（均西坡村）；6号塘7.2/0.40/0.10、10号塘7.4/0.20/0.10（信坡村）；7号塘7.2/0.90/0.05、8号塘7.4/0.90/0.10、9号塘7.2/0.90/0.10（南排坡），三项均正常，1号塘pH8.6经人眼复核确认；其余塘口待补测；10月14日：协助马总放石斑进塘；10月23日积炭素累计用到100包，今天拉了33包；10月25日：送动保和药物，客情维护。</t>
         </is>
       </c>
       <c r="G70" t="n">

--- a/数据/养殖客户档案.xlsx
+++ b/数据/养殖客户档案.xlsx
@@ -3560,7 +3560,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>9月10日/9月28日/10月13日/10月16日/10月23日</t>
+          <t>9月10日/9月28日/10月13日/10月16日/10月23日/10月27日</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3575,11 +3575,11 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>9月10日用户不在，电话联系测水打样；9月28日测水打样七两左右，鱼肥满度很好；10月13日打样：鱼一斤三左右，长势好；10月16日走访，今日未打样，约定10月23日再来打样测水（底下那口塘）；10月23日打样测水：塘号结构1号苗塘、2号中间那口、3号路边塘；1号塘10月21日放苗14万尾、亚盐偏高0.3左右踩报警线；2号塘条均八两、存塘鱼7万尾；3号塘条均预计1.4斤以上（10月13日1.35斤）、存塘未知；2号3号水质正常</t>
+          <t>9月10日用户不在，电话联系测水打样；9月28日测水打样七两左右，鱼肥满度很好；10月13日打样：鱼一斤三左右，长势好；10月16日走访，今日未打样，约定10月23日再来打样测水（底下那口塘）；10月23日打样测水：塘号结构1号苗塘、2号中间那口、3号路边塘；1号塘10月21日放苗14万尾、亚盐偏高0.3左右踩报警线；2号塘条均八两、存塘鱼7万尾；3号塘条均预计1.4斤以上（10月13日1.35斤）、存塘未知；2号3号水质正常；10月27日测水：1号苗塘经硝硝乐（同音变体：消消乐）处理，原亚盐0.3+踩报警线已降至正常；2号塘亚盐0.25（临界，接近0.3警戒线），预计约20天出鱼；3号塘本次未测。用户想培育光合菌。</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H69" t="n">
         <v>45</v>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>10月22日/10月23日</t>
+          <t>10月22日/10月23日/10月27日</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6177,11 +6177,11 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>10月22日走访：老板休息，约次日看抓鱼；10月23日抓鱼回访：一号塘包产35（死鱼严重）、二号塘包产38、三号塘未抓完；老徐自述包产不过40系鱼苗问题</t>
+          <t>10月22日走访：老板休息，约次日看抓鱼；10月23日抓鱼回访：一号塘包产35（死鱼严重）、二号塘包产38、三号塘未抓完；老徐自述包产不过40系鱼苗问题；10月27日出鱼回访：最后一口塘未干塘、已抓8万多、包产约39；用户反馈鱼苗质量太低，与包产不过40系鱼苗问题印证</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H126" t="n">
         <v>20</v>

--- a/数据/养殖客户档案.xlsx
+++ b/数据/养殖客户档案.xlsx
@@ -3606,7 +3606,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>9月10日/9月21日/9月23日/9月27日/9月28日/10月13日/10月14日/10月23日/10月25日</t>
+          <t>9月10日/9月21日/9月23日/9月27日/9月28日/10月13日/10月14日/10月23日/10月25日/10月27日</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>9月10日希望建设光合菌扩培系统；9月21日有扩培光合菌需求，已自行联系吴老师对接；9月23日帮助用户泼洒我司动保；9月27日用完我司乳酸菌+芽孢分解菌后四天，鱼吃料情况稍差，测水正常，过几天不正常吃料则打样解剖；9月28日口塘测水打样五两，六号塘情况稍差、其余均良好；10月13日基地客勤+测水10口塘：3号塘7.0/0.2/0.10、5号塘7.4/0.2/0.005、4号塘7.2/0.2/0.005、2号塘7.4/0.2/0.10、1号塘8.6/0.2/0.005（均西坡村）；6号塘7.2/0.40/0.10、10号塘7.4/0.20/0.10（信坡村）；7号塘7.2/0.90/0.05、8号塘7.4/0.90/0.10、9号塘7.2/0.90/0.10（南排坡），三项均正常，1号塘pH8.6经人眼复核确认；其余塘口待补测；10月14日：协助马总放石斑进塘；10月23日积炭素累计用到100包，今天拉了33包；10月25日：送动保和药物，客情维护。</t>
+          <t>9月10日希望建设光合菌扩培系统；9月21日有扩培光合菌需求，已自行联系吴老师对接；9月23日帮助用户泼洒我司动保；9月27日用完我司乳酸菌+芽孢分解菌后四天，鱼吃料情况稍差，测水正常，过几天不正常吃料则打样解剖；9月28日口塘测水打样五两，六号塘情况稍差、其余均良好；10月13日基地客勤+测水10口塘：3号塘7.0/0.2/0.10、5号塘7.4/0.2/0.005、4号塘7.2/0.2/0.005、2号塘7.4/0.2/0.10、1号塘8.6/0.2/0.005（均西坡村）；6号塘7.2/0.40/0.10、10号塘7.4/0.20/0.10（信坡村）；7号塘7.2/0.90/0.05、8号塘7.4/0.90/0.10、9号塘7.2/0.90/0.10（南排坡），三项均正常，1号塘pH8.6经人眼复核确认；其余塘口待补测；10月14日：协助马总放石斑进塘；10月23日积炭素累计用到100包，今天拉了33包；10月25日：送动保和药物，客情维护。；10月27日测水：西坡村1/2/3/4/5号塘，pH、氨氮、亚盐均正常，无异常。</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H70" t="n">
         <v>45</v>

--- a/数据/养殖客户档案.xlsx
+++ b/数据/养殖客户档案.xlsx
@@ -3565,7 +3565,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9912（我司；非全程用）</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1053（非全程用）</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">

--- a/数据/养殖客户档案.xlsx
+++ b/数据/养殖客户档案.xlsx
@@ -3575,7 +3575,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>9月10日用户不在，电话联系测水打样；9月28日测水打样七两左右，鱼肥满度很好；10月13日打样：鱼一斤三左右，长势好；10月16日走访，今日未打样，约定10月23日再来打样测水（底下那口塘）；10月23日打样测水：塘号结构1号苗塘、2号中间那口、3号路边塘；1号塘10月21日放苗14万尾、亚盐偏高0.3左右踩报警线；2号塘条均八两、存塘鱼7万尾；3号塘条均预计1.4斤以上（10月13日1.35斤）、存塘未知；2号3号水质正常；10月27日测水：1号苗塘经硝硝乐（同音变体：消消乐）处理，原亚盐0.3+踩报警线已降至正常；2号塘亚盐0.25（临界，接近0.3警戒线），预计约20天出鱼；3号塘本次未测。用户想培育光合菌。</t>
+          <t>9月10日用户不在，电话联系测水打样；9月28日测水打样七两左右，鱼肥满度很好；10月13日打样：鱼一斤三左右，长势好；10月16日走访，今日未打样，约定10月23日再来打样测水（底下那口塘）；10月23日打样测水：塘号结构1号苗塘、2号中间那口、3号路边塘；1号塘10月21日放苗14万尾、亚盐偏高0.3左右踩报警线；2号塘条均八两、存塘鱼7万尾；3号塘条均预计1.4斤以上（10月13日1.35斤）、存塘未知；2号3号水质正常；10月27日测水（比色卡目视实测，铺前镇华兰村）：1号苗塘pH7.1/氨氮0.20/亚盐0.15（硝硝乐处理后正常）、2号塘pH6.9/氨氮0/亚盐0.20（临界临近0.3警戒线，预计约20天出鱼）、3号塘pH7.2/氨氮0/亚盐0.05（原未测补测）；用户想培育光合菌。</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>9月10日希望建设光合菌扩培系统；9月21日有扩培光合菌需求，已自行联系吴老师对接；9月23日帮助用户泼洒我司动保；9月27日用完我司乳酸菌+芽孢分解菌后四天，鱼吃料情况稍差，测水正常，过几天不正常吃料则打样解剖；9月28日口塘测水打样五两，六号塘情况稍差、其余均良好；10月13日基地客勤+测水10口塘：3号塘7.0/0.2/0.10、5号塘7.4/0.2/0.005、4号塘7.2/0.2/0.005、2号塘7.4/0.2/0.10、1号塘8.6/0.2/0.005（均西坡村）；6号塘7.2/0.40/0.10、10号塘7.4/0.20/0.10（信坡村）；7号塘7.2/0.90/0.05、8号塘7.4/0.90/0.10、9号塘7.2/0.90/0.10（南排坡），三项均正常，1号塘pH8.6经人眼复核确认；其余塘口待补测；10月14日：协助马总放石斑进塘；10月23日积炭素累计用到100包，今天拉了33包；10月25日：送动保和药物，客情维护。；10月27日测水：西坡村1/2/3/4/5号塘，pH、氨氮、亚盐均正常，无异常。</t>
+          <t>9月10日希望建设光合菌扩培系统；9月21日有扩培光合菌需求，已自行联系吴老师对接；9月23日帮助用户泼洒我司动保；9月27日用完我司乳酸菌+芽孢分解菌后四天，鱼吃料情况稍差，测水正常，过几天不正常吃料则打样解剖；9月28日口塘测水打样五两，六号塘情况稍差、其余均良好；10月13日基地客勤+测水10口塘：3号塘7.0/0.2/0.10、5号塘7.4/0.2/0.005、4号塘7.2/0.2/0.005、2号塘7.4/0.2/0.10、1号塘8.6/0.2/0.005（均西坡村）；6号塘7.2/0.40/0.10、10号塘7.4/0.20/0.10（信坡村）；7号塘7.2/0.90/0.05、8号塘7.4/0.90/0.10、9号塘7.2/0.90/0.10（南排坡），三项均正常，1号塘pH8.6经人眼复核确认；其余塘口待补测；10月14日：协助马总放石斑进塘；10月23日积炭素累计用到100包，今天拉了33包；10月25日：送动保和药物，客情维护。10月27日测水（比色卡目视实测）：1号塘(罗豆农场猪场)pH7.2/氨氮0.20/亚盐0、2号塘(西坡村)pH7.4/氨氮0.60/亚盐0.10(五口最高，回访重点)、3号塘pH7.2/氨氮0.60/亚盐0.005、4号塘pH7.0/氨氮0.20/亚盐0、5号塘pH7.2/氨氮0.20/亚盐0.01；全部在安全线内。</t>
         </is>
       </c>
       <c r="G70" t="n">

--- a/数据/养殖客户档案.xlsx
+++ b/数据/养殖客户档案.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J127"/>
+  <dimension ref="A1:J129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6243,6 +6243,98 @@
         </is>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>吴杨松</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>10月7日</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>歌颂</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>冯学新</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>现用歌颂饲料，跟冯学新拿现金料105元/包（正常价121元）；早年用过通威沉水颗粒料，后用过百洋（反馈一般），现转歌颂，元旦前抓鱼；自"建一"出来后一直跟冯学新拿料。</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>1</v>
+      </c>
+      <c r="H128" t="n">
+        <v>25</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>C 有潜力</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>早年用过通威沉水颗粒料（有通威基础），现跟冯学新拿歌颂现金料105元/包、价格敏感；以性价比+测水服务切入争取试料</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>韩利光</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>10月7日</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>金长城、百洋、海大</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>昌盛</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>跟昌盛（其同学）拿料，现混用金长城+百洋+海大；塘口正在修投料机，此前停养一段时间，现打算恢复养殖；有问到过通威包产如何，已推荐我司饲料。</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>1</v>
+      </c>
+      <c r="H129" t="n">
+        <v>25</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>C 有潜力</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>恢复养殖阶段主动问到通威包产（有意向），现混用金长城+百洋+海大跟昌盛拿料，已推荐我司饲料</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
